--- a/Data/EC/NIT-9009540403.xlsx
+++ b/Data/EC/NIT-9009540403.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9704C434-2D6D-4134-8EC2-7CAAB81671B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56D9AA45-F820-45D4-AD95-AEB4804017EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{035DB9EE-C371-4802-BB74-F9EDA5A3CF18}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E7B928A0-979D-4DD6-B7C8-09BE7DFB098D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -71,90 +71,90 @@
     <t>LUIS RAFAEL ROCA ZABALETA</t>
   </si>
   <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
+    <t>1705</t>
+  </si>
+  <si>
+    <t>1704</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>1701</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>1609</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
     <t>1607</t>
   </si>
   <si>
-    <t>1608</t>
-  </si>
-  <si>
-    <t>1609</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>1611</t>
-  </si>
-  <si>
-    <t>1612</t>
-  </si>
-  <si>
-    <t>1701</t>
-  </si>
-  <si>
-    <t>1702</t>
-  </si>
-  <si>
-    <t>1703</t>
-  </si>
-  <si>
-    <t>1704</t>
-  </si>
-  <si>
-    <t>1705</t>
-  </si>
-  <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
     <t>1143346716</t>
   </si>
   <si>
@@ -170,178 +170,178 @@
     <t>ANTONY CABARCAS MORENO</t>
   </si>
   <si>
+    <t>2411</t>
+  </si>
+  <si>
+    <t>2410</t>
+  </si>
+  <si>
+    <t>2409</t>
+  </si>
+  <si>
+    <t>2408</t>
+  </si>
+  <si>
+    <t>2407</t>
+  </si>
+  <si>
+    <t>2406</t>
+  </si>
+  <si>
+    <t>2405</t>
+  </si>
+  <si>
+    <t>2404</t>
+  </si>
+  <si>
+    <t>2403</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>2401</t>
+  </si>
+  <si>
+    <t>2312</t>
+  </si>
+  <si>
+    <t>2311</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>2309</t>
+  </si>
+  <si>
+    <t>2308</t>
+  </si>
+  <si>
+    <t>2307</t>
+  </si>
+  <si>
+    <t>2306</t>
+  </si>
+  <si>
+    <t>2305</t>
+  </si>
+  <si>
+    <t>2304</t>
+  </si>
+  <si>
+    <t>2303</t>
+  </si>
+  <si>
+    <t>2302</t>
+  </si>
+  <si>
+    <t>2301</t>
+  </si>
+  <si>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>2209</t>
+  </si>
+  <si>
+    <t>2208</t>
+  </si>
+  <si>
+    <t>2207</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
     <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>2207</t>
-  </si>
-  <si>
-    <t>2208</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>2212</t>
-  </si>
-  <si>
-    <t>2301</t>
-  </si>
-  <si>
-    <t>2302</t>
-  </si>
-  <si>
-    <t>2303</t>
-  </si>
-  <si>
-    <t>2304</t>
-  </si>
-  <si>
-    <t>2305</t>
-  </si>
-  <si>
-    <t>2306</t>
-  </si>
-  <si>
-    <t>2307</t>
-  </si>
-  <si>
-    <t>2308</t>
-  </si>
-  <si>
-    <t>2309</t>
-  </si>
-  <si>
-    <t>2310</t>
-  </si>
-  <si>
-    <t>2311</t>
-  </si>
-  <si>
-    <t>2312</t>
-  </si>
-  <si>
-    <t>2401</t>
-  </si>
-  <si>
-    <t>2402</t>
-  </si>
-  <si>
-    <t>2403</t>
-  </si>
-  <si>
-    <t>2404</t>
-  </si>
-  <si>
-    <t>2405</t>
-  </si>
-  <si>
-    <t>2406</t>
-  </si>
-  <si>
-    <t>2407</t>
-  </si>
-  <si>
-    <t>2408</t>
-  </si>
-  <si>
-    <t>2409</t>
-  </si>
-  <si>
-    <t>2410</t>
-  </si>
-  <si>
-    <t>2411</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -385,7 +385,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -440,9 +440,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -455,7 +453,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -655,23 +655,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -699,10 +699,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -740,22 +740,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>496450</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>259200</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7B71760-6561-7E81-262F-F183A23C5AA1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD7C9610-D6DC-596B-C233-38361F627C9D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -777,7 +777,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="750450" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1106,23 +1106,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DACCD2A9-14C0-439B-8825-9E1363DB1A31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{654A9820-803E-4602-A456-8079C95E5FD8}">
   <dimension ref="B2:J109"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="16.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1135,7 +1135,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1146,7 +1146,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1157,7 +1157,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1168,8 +1168,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1"/>
-    <row r="7" spans="2:10">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>103</v>
       </c>
@@ -1184,8 +1184,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1"/>
-    <row r="9" spans="2:10">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1200,8 +1200,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1"/>
-    <row r="11" spans="2:10">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>104</v>
       </c>
@@ -1216,8 +1216,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1"/>
-    <row r="13" spans="2:10">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>105</v>
       </c>
@@ -1236,7 +1236,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>29200</v>
+        <v>23958</v>
       </c>
       <c r="G16" s="18">
         <v>781242</v>
@@ -1288,7 +1288,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="18">
-        <v>29200</v>
+        <v>31249</v>
       </c>
       <c r="G17" s="18">
         <v>781242</v>
@@ -1311,7 +1311,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1334,7 +1334,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1357,7 +1357,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1380,7 +1380,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1403,7 +1403,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1426,7 +1426,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1449,7 +1449,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1472,7 +1472,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1495,7 +1495,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1541,7 +1541,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1564,7 +1564,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1587,7 +1587,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1610,7 +1610,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1633,7 +1633,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1656,7 +1656,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1679,7 +1679,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1702,7 +1702,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1725,7 +1725,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1748,7 +1748,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1771,7 +1771,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1794,7 +1794,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1817,7 +1817,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1840,7 +1840,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1863,7 +1863,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>37</v>
       </c>
       <c r="F42" s="18">
-        <v>31249</v>
+        <v>29200</v>
       </c>
       <c r="G42" s="18">
         <v>781242</v>
@@ -1886,7 +1886,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>38</v>
       </c>
       <c r="F43" s="18">
-        <v>23958</v>
+        <v>29200</v>
       </c>
       <c r="G43" s="18">
         <v>781242</v>
@@ -1909,7 +1909,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1932,7 +1932,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1943,10 +1943,10 @@
         <v>43</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F45" s="18">
-        <v>33125</v>
+        <v>15458</v>
       </c>
       <c r="G45" s="18">
         <v>828116</v>
@@ -1955,7 +1955,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>43</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F46" s="18">
         <v>33125</v>
@@ -1978,7 +1978,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>43</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F47" s="18">
         <v>33125</v>
@@ -2001,7 +2001,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>43</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F48" s="18">
         <v>33125</v>
@@ -2024,7 +2024,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>43</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F49" s="18">
         <v>33125</v>
@@ -2047,7 +2047,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>43</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F50" s="18">
         <v>33125</v>
@@ -2070,7 +2070,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>43</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F51" s="18">
         <v>33125</v>
@@ -2093,7 +2093,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>43</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F52" s="18">
         <v>33125</v>
@@ -2116,7 +2116,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>43</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F53" s="18">
         <v>33125</v>
@@ -2139,7 +2139,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>43</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F54" s="18">
         <v>33125</v>
@@ -2162,7 +2162,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>43</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F55" s="18">
         <v>33125</v>
@@ -2185,7 +2185,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>43</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F56" s="18">
         <v>33125</v>
@@ -2208,7 +2208,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>43</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F57" s="18">
         <v>33125</v>
@@ -2231,7 +2231,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>43</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F58" s="18">
         <v>33125</v>
@@ -2254,7 +2254,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>43</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F59" s="18">
         <v>33125</v>
@@ -2277,7 +2277,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>43</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F60" s="18">
         <v>33125</v>
@@ -2300,7 +2300,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>43</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F61" s="18">
         <v>33125</v>
@@ -2323,7 +2323,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>43</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F62" s="18">
         <v>33125</v>
@@ -2346,7 +2346,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>43</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F63" s="18">
         <v>33125</v>
@@ -2369,7 +2369,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>43</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F64" s="18">
         <v>33125</v>
@@ -2392,7 +2392,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>43</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F65" s="18">
         <v>33125</v>
@@ -2415,7 +2415,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>43</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F66" s="18">
         <v>33125</v>
@@ -2438,7 +2438,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>43</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F67" s="18">
         <v>33125</v>
@@ -2461,7 +2461,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>43</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F68" s="18">
         <v>33125</v>
@@ -2484,7 +2484,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>43</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F69" s="18">
         <v>33125</v>
@@ -2507,7 +2507,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>43</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F70" s="18">
         <v>33125</v>
@@ -2530,7 +2530,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>43</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F71" s="18">
         <v>33125</v>
@@ -2553,7 +2553,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>43</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F72" s="18">
         <v>33125</v>
@@ -2576,7 +2576,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>43</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F73" s="18">
         <v>33125</v>
@@ -2599,7 +2599,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>43</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F74" s="18">
         <v>33125</v>
@@ -2622,7 +2622,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>43</v>
       </c>
       <c r="E75" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F75" s="18">
         <v>33125</v>
@@ -2645,7 +2645,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>43</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F76" s="18">
         <v>33125</v>
@@ -2668,7 +2668,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>43</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F77" s="18">
         <v>33125</v>
@@ -2691,7 +2691,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>43</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F78" s="18">
         <v>33125</v>
@@ -2714,7 +2714,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>43</v>
       </c>
       <c r="E79" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F79" s="18">
         <v>33125</v>
@@ -2737,7 +2737,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>43</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F80" s="18">
         <v>33125</v>
@@ -2760,7 +2760,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2771,7 +2771,7 @@
         <v>43</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F81" s="18">
         <v>33125</v>
@@ -2783,7 +2783,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>43</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F82" s="18">
         <v>33125</v>
@@ -2806,7 +2806,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>43</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F83" s="18">
         <v>33125</v>
@@ -2829,7 +2829,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>43</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F84" s="18">
         <v>33125</v>
@@ -2852,7 +2852,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>43</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F85" s="18">
         <v>33125</v>
@@ -2875,7 +2875,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>43</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F86" s="18">
         <v>33125</v>
@@ -2898,7 +2898,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>43</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F87" s="18">
         <v>33125</v>
@@ -2921,7 +2921,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>43</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F88" s="18">
         <v>33125</v>
@@ -2944,7 +2944,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>43</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F89" s="18">
         <v>33125</v>
@@ -2967,7 +2967,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>43</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F90" s="18">
         <v>33125</v>
@@ -2990,7 +2990,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>43</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F91" s="18">
         <v>33125</v>
@@ -3013,7 +3013,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>43</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F92" s="18">
         <v>33125</v>
@@ -3036,7 +3036,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>43</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F93" s="18">
         <v>33125</v>
@@ -3059,7 +3059,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>43</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F94" s="18">
         <v>33125</v>
@@ -3082,7 +3082,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>43</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F95" s="18">
         <v>33125</v>
@@ -3105,7 +3105,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>43</v>
       </c>
       <c r="E96" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F96" s="18">
         <v>33125</v>
@@ -3128,7 +3128,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>43</v>
       </c>
       <c r="E97" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F97" s="18">
         <v>33125</v>
@@ -3151,7 +3151,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>43</v>
       </c>
       <c r="E98" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F98" s="18">
         <v>33125</v>
@@ -3174,7 +3174,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>43</v>
       </c>
       <c r="E99" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F99" s="18">
         <v>33125</v>
@@ -3197,7 +3197,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>43</v>
       </c>
       <c r="E100" s="16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F100" s="18">
         <v>33125</v>
@@ -3220,7 +3220,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>43</v>
       </c>
       <c r="E101" s="16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F101" s="18">
         <v>33125</v>
@@ -3243,7 +3243,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>43</v>
       </c>
       <c r="E102" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F102" s="18">
         <v>33125</v>
@@ -3266,7 +3266,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="21" t="s">
         <v>8</v>
       </c>
@@ -3277,10 +3277,10 @@
         <v>43</v>
       </c>
       <c r="E103" s="22" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="F103" s="24">
-        <v>15458</v>
+        <v>33125</v>
       </c>
       <c r="G103" s="24">
         <v>828116</v>
@@ -3289,7 +3289,7 @@
       <c r="I103" s="25"/>
       <c r="J103" s="26"/>
     </row>
-    <row r="108" spans="2:10">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="32" t="s">
         <v>111</v>
       </c>
@@ -3300,7 +3300,7 @@
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
     </row>
-    <row r="109" spans="2:10">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="32" t="s">
         <v>110</v>
       </c>
